--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending3.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending3.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_结局3" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="399">
   <si>
     <t>ID</t>
   </si>
@@ -466,6 +466,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>说着，他朝被按在地上的女人投去一个带着怨毒的眼神，似乎在替他的</t>
     </r>
     <r>
@@ -577,6 +582,9 @@
     <t>black</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>parallel(shake(screen,10,0.5);playsfx(GunShot))</t>
   </si>
   <si>
@@ -649,6 +657,12 @@
     <t>达成结局——【弃翼者的陨落】</t>
   </si>
   <si>
+    <t>22 the_mountain-horror</t>
+  </si>
+  <si>
+    <t>unlockending(Ending1)&amp;unlockmusic(Music22)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=52</t>
   </si>
   <si>
@@ -659,6 +673,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -3796,7 +3815,7 @@
         <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
@@ -4463,19 +4482,18 @@
         <v>164</v>
       </c>
       <c r="I51" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51"/>
+        <v>165</v>
+      </c>
       <c r="K51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4493,7 +4511,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4508,12 +4526,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" ht="54" spans="1:12">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4531,7 +4549,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4543,15 +4561,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" ht="54" spans="1:12">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4569,7 +4587,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4580,14 +4598,13 @@
       <c r="J54" t="s">
         <v>15</v>
       </c>
-      <c r="K54"/>
       <c r="L54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" ht="30" spans="1:12">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4605,7 +4622,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4620,12 +4637,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" ht="70.5" spans="1:12">
       <c r="A56" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4643,7 +4660,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H56" t="s">
         <v>164</v>
@@ -4658,12 +4675,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4681,7 +4698,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4693,15 +4710,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L57" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" ht="30" spans="1:12">
       <c r="A58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4719,27 +4736,27 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
       </c>
       <c r="I58" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="J58" t="s">
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
       <c r="L58" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" ht="150" spans="1:12">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4757,7 +4774,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4772,12 +4789,12 @@
         <v>140</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" ht="54" spans="1:12">
       <c r="A60" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4795,7 +4812,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4807,15 +4824,15 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L60" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" ht="90" spans="1:12">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4833,7 +4850,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4844,14 +4861,13 @@
       <c r="J61" t="s">
         <v>15</v>
       </c>
-      <c r="K61"/>
       <c r="L61" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" ht="58.5" spans="1:12">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4869,7 +4885,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4884,12 +4900,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4907,7 +4923,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4922,12 +4938,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" ht="28.5" spans="1:12">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -4945,7 +4961,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -4957,15 +4973,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L64" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" ht="28.5" spans="1:12">
       <c r="A65" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B65" t="s">
         <v>22</v>
@@ -4983,7 +4999,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -4998,12 +5014,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5041,7 +5057,7 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5079,7 +5095,7 @@
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5097,7 +5113,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5109,10 +5125,10 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L68" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -5133,47 +5149,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -5181,15 +5197,15 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B8" t="s">
         <v>104</v>
@@ -5197,7 +5213,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B9" t="s">
         <v>92</v>
@@ -5205,50 +5221,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5270,616 +5286,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C8" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E9" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D10" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E10" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F10" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D11" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B12" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C12" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D12" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E12" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F12" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C13" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E13" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B14" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C14" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D14" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C15" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B16" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C16" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D16" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E16" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F16" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B17" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D17" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E17" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F17" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B18" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C18" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D18" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E18" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F18" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B19" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C19" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D19" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F19" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B20" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C20" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D20" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E20" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F20" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B21" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C21" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D21" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E21" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F21" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B22" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C22" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D22" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E22" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F22" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B23" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C23" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D23" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E23" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F23" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B24" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C24" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D24" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E24" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F24" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B25" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C25" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D25" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E25" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F25" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B26" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C26" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D26" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E26" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F26" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B27" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C27" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D27" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E27" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F27" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B28" t="s">
+        <v>381</v>
+      </c>
+      <c r="C28" t="s">
+        <v>382</v>
+      </c>
+      <c r="D28" t="s">
         <v>378</v>
       </c>
-      <c r="C28" t="s">
-        <v>379</v>
-      </c>
-      <c r="D28" t="s">
-        <v>375</v>
-      </c>
       <c r="E28" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F28" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B29" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C29" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D29" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E29" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F29" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B30" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C30" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D30" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E30" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F30" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B31" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C31" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D31" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
